--- a/seed/Application Saraillon (1).xlsx
+++ b/seed/Application Saraillon (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.zinzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Documents\saraillon\seed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5121B9-DC96-44FF-B16C-C1F71218786D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2A83A2-7F9D-4261-B2F0-DF75D6ADB793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Programme" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="126">
   <si>
     <t>Jour</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Marseille : Calanques, puis Friche (ascenseur panne). Soirée Constellations</t>
   </si>
   <si>
-    <t>Déjeuner (pic nic) + Dîner (sur place)</t>
-  </si>
-  <si>
     <t>Oui</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>https://forms.gle/7F35tvEUbPNTLvh5A</t>
   </si>
   <si>
-    <t>Déjeuner (repas sur le bateau)</t>
-  </si>
-  <si>
     <t>Vêtement coupe-vent, casquette, crème solaire</t>
   </si>
   <si>
@@ -221,9 +215,6 @@
     <t>Anse Méjean</t>
   </si>
   <si>
-    <t>Déjeuner (pic nic plage)</t>
-  </si>
-  <si>
     <t>Maillot, serviette, chaussons d’eau (optionnel), crème solaire</t>
   </si>
   <si>
@@ -239,9 +230,6 @@
     <t>https://forms.gle/TjtfUzamMA5pKdfv9</t>
   </si>
   <si>
-    <t>Déjeuner (après)</t>
-  </si>
-  <si>
     <t>Casque (souvent fourni)</t>
   </si>
   <si>
@@ -296,9 +284,6 @@
     <t>10h30-18h00</t>
   </si>
   <si>
-    <t>Déjeuner + Dîner (avant réveillon)</t>
-  </si>
-  <si>
     <t>(selon atelier)</t>
   </si>
   <si>
@@ -323,9 +308,6 @@
     <t>Piscine</t>
   </si>
   <si>
-    <t>Déjeuner (léger) + Dîner (clôture)</t>
-  </si>
-  <si>
     <t>Maillot, serviette, crème solaire</t>
   </si>
   <si>
@@ -411,6 +393,15 @@
   </si>
   <si>
     <t>https://... (message audio)</t>
+  </si>
+  <si>
+    <t>Déjeuner (panier repas) + Dîner (sur place)</t>
+  </si>
+  <si>
+    <t>Déjeuner</t>
+  </si>
+  <si>
+    <t>Déjeuner + Dîner au restaurant</t>
   </si>
 </sst>
 </file>
@@ -734,10 +725,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
     <col min="4" max="4" width="46.85546875" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1">
@@ -790,7 +783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="15">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -838,7 +831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="15">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -858,16 +851,16 @@
         <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>23</v>
@@ -876,40 +869,40 @@
         <v>24</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:16" ht="15">
+      <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="H4" s="2" t="s">
         <v>22</v>
       </c>
@@ -917,7 +910,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>23</v>
@@ -938,28 +931,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="15">
       <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
@@ -967,7 +960,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>23</v>
@@ -976,39 +969,39 @@
         <v>24</v>
       </c>
       <c r="M5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:16" ht="15">
+      <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>22</v>
@@ -1017,7 +1010,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>23</v>
@@ -1026,81 +1019,81 @@
         <v>24</v>
       </c>
       <c r="M6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:16" ht="15">
+      <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15">
+      <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1108,7 +1101,7 @@
         <v>24</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>22</v>
@@ -1117,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>23</v>
@@ -1126,39 +1119,39 @@
         <v>24</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15">
+      <c r="A9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>22</v>
@@ -1167,98 +1160,98 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:16" ht="15">
+      <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="N10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15">
+      <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>22</v>
@@ -1273,10 +1266,10 @@
         <v>23</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>20</v>
@@ -1288,18 +1281,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" ht="15">
       <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
@@ -1308,7 +1301,7 @@
         <v>24</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>22</v>
@@ -1317,16 +1310,16 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>20</v>
@@ -1338,18 +1331,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="15">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>20</v>
@@ -1358,7 +1351,7 @@
         <v>24</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>22</v>
@@ -1388,18 +1381,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" ht="15">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>20</v>
@@ -1408,7 +1401,7 @@
         <v>24</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>22</v>
@@ -1417,7 +1410,7 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>23</v>
@@ -1426,30 +1419,30 @@
         <v>24</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" ht="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>20</v>
@@ -1467,7 +1460,7 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>23</v>
@@ -1505,32 +1498,32 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="59.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" ht="15">
       <c r="A3" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15">
       <c r="A4" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="12.75">
       <c r="A5" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1544,36 +1537,36 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1587,54 +1580,54 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15">
+      <c r="A2" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15">
+      <c r="A3" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15">
+      <c r="A4" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15">
+      <c r="A5" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15">
+      <c r="A6" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15">
+      <c r="A7" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+    <row r="8" spans="1:1" ht="15">
+      <c r="A8" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
+    <row r="9" spans="1:1" ht="15">
+      <c r="A9" s="3" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1648,30 +1641,30 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15">
       <c r="A2" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
